--- a/artfynd/A 18569-2025 artfynd.xlsx
+++ b/artfynd/A 18569-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124282089</v>
+        <v>124282403</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bräcke kommun, Bräcke kommun, Jmt</t>
+          <t>Öramyran, Öramyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527679</v>
+        <v>527748</v>
       </c>
       <c r="R2" t="n">
-        <v>6963934</v>
+        <v>6963833</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,27 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>08:40</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>08:40</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hackspår, äldre.</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,48 +761,23 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124282327</v>
+        <v>124282371</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -862,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527721</v>
+        <v>527779</v>
       </c>
       <c r="R3" t="n">
-        <v>6963875</v>
+        <v>6963815</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -907,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,22 +881,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -959,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124282371</v>
+        <v>124282089</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -975,37 +930,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öramyran, Öramyran, Jmt</t>
+          <t>Bräcke kommun, Bräcke kommun, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527779</v>
+        <v>527679</v>
       </c>
       <c r="R4" t="n">
-        <v>6963815</v>
+        <v>6963934</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1034,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,7 +1004,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hackspår, äldre.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1058,7 +1023,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1073,12 +1038,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1198,7 +1163,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124282403</v>
+        <v>124282327</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1238,13 +1203,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527748</v>
+        <v>527721</v>
       </c>
       <c r="R6" t="n">
-        <v>6963833</v>
+        <v>6963875</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1268,12 +1233,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,16 +1259,41 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 18569-2025 artfynd.xlsx
+++ b/artfynd/A 18569-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124282403</v>
+        <v>124282089</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öramyran, Öramyran, Jmt</t>
+          <t>Bräcke kommun, Bräcke kommun, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527748</v>
+        <v>527679</v>
       </c>
       <c r="R2" t="n">
-        <v>6963833</v>
+        <v>6963934</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +750,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hackspår, äldre.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,23 +781,48 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124282371</v>
+        <v>124282327</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -817,13 +862,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527779</v>
+        <v>527721</v>
       </c>
       <c r="R3" t="n">
-        <v>6963815</v>
+        <v>6963875</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +897,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +907,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,22 +926,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -914,10 +959,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124282089</v>
+        <v>124282371</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,42 +975,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bräcke kommun, Bräcke kommun, Jmt</t>
+          <t>Öramyran, Öramyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527679</v>
+        <v>527779</v>
       </c>
       <c r="R4" t="n">
-        <v>6963934</v>
+        <v>6963815</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,12 +1044,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:40</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hackspår, äldre.</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,7 +1058,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1038,12 +1073,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1061,7 +1096,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124282307</v>
+        <v>124282403</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1101,10 +1136,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527724</v>
+        <v>527748</v>
       </c>
       <c r="R5" t="n">
-        <v>6963869</v>
+        <v>6963833</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1163,7 +1198,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124282327</v>
+        <v>124282307</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1203,13 +1238,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527721</v>
+        <v>527724</v>
       </c>
       <c r="R6" t="n">
-        <v>6963875</v>
+        <v>6963869</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,22 +1268,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>08:46</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>08:46</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,41 +1284,16 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 18569-2025 artfynd.xlsx
+++ b/artfynd/A 18569-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124282089</v>
+        <v>124282307</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bräcke kommun, Bräcke kommun, Jmt</t>
+          <t>Öramyran, Öramyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527679</v>
+        <v>527724</v>
       </c>
       <c r="R2" t="n">
-        <v>6963934</v>
+        <v>6963869</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,27 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>08:40</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>08:40</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hackspår, äldre.</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,41 +761,16 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -1096,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124282403</v>
+        <v>124282089</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1112,37 +1067,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öramyran, Öramyran, Jmt</t>
+          <t>Bräcke kommun, Bräcke kommun, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527748</v>
+        <v>527679</v>
       </c>
       <c r="R5" t="n">
-        <v>6963833</v>
+        <v>6963934</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1166,12 +1126,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hackspår, äldre.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1182,23 +1157,48 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124282307</v>
+        <v>124282403</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527724</v>
+        <v>527748</v>
       </c>
       <c r="R6" t="n">
-        <v>6963869</v>
+        <v>6963833</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 18569-2025 artfynd.xlsx
+++ b/artfynd/A 18569-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124282307</v>
+        <v>124282327</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527724</v>
+        <v>527721</v>
       </c>
       <c r="R2" t="n">
-        <v>6963869</v>
+        <v>6963875</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,26 +771,51 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124282327</v>
+        <v>124282089</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +828,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öramyran, Öramyran, Jmt</t>
+          <t>Bräcke kommun, Bräcke kommun, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527721</v>
+        <v>527679</v>
       </c>
       <c r="R3" t="n">
-        <v>6963875</v>
+        <v>6963934</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +902,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hackspår, äldre.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,27 +921,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -914,7 +959,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124282371</v>
+        <v>124282403</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -954,13 +999,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527779</v>
+        <v>527748</v>
       </c>
       <c r="R4" t="n">
-        <v>6963815</v>
+        <v>6963833</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,22 +1029,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>08:49</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>08:49</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,51 +1045,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124282089</v>
+        <v>124282371</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,42 +1077,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bräcke kommun, Bräcke kommun, Jmt</t>
+          <t>Öramyran, Öramyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527679</v>
+        <v>527779</v>
       </c>
       <c r="R5" t="n">
-        <v>6963934</v>
+        <v>6963815</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,7 +1136,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1141,12 +1146,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:40</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hackspår, äldre.</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124282403</v>
+        <v>124282307</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527748</v>
+        <v>527724</v>
       </c>
       <c r="R6" t="n">
-        <v>6963833</v>
+        <v>6963869</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 18569-2025 artfynd.xlsx
+++ b/artfynd/A 18569-2025 artfynd.xlsx
@@ -812,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124282089</v>
+        <v>124282403</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,42 +828,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bräcke kommun, Bräcke kommun, Jmt</t>
+          <t>Öramyran, Öramyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527679</v>
+        <v>527748</v>
       </c>
       <c r="R3" t="n">
-        <v>6963934</v>
+        <v>6963833</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,27 +882,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>08:40</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>08:40</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hackspår, äldre.</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,51 +898,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124282403</v>
+        <v>124282089</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -975,37 +930,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öramyran, Öramyran, Jmt</t>
+          <t>Bräcke kommun, Bräcke kommun, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527748</v>
+        <v>527679</v>
       </c>
       <c r="R4" t="n">
-        <v>6963833</v>
+        <v>6963934</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1029,12 +989,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hackspår, äldre.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,16 +1020,41 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 18569-2025 artfynd.xlsx
+++ b/artfynd/A 18569-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124282327</v>
+        <v>124282403</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527721</v>
+        <v>527748</v>
       </c>
       <c r="R2" t="n">
-        <v>6963875</v>
+        <v>6963833</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>08:46</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>08:46</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,51 +761,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124282403</v>
+        <v>124282089</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,37 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öramyran, Öramyran, Jmt</t>
+          <t>Bräcke kommun, Bräcke kommun, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527748</v>
+        <v>527679</v>
       </c>
       <c r="R3" t="n">
-        <v>6963833</v>
+        <v>6963934</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,12 +852,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hackspår, äldre.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,26 +883,51 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124282089</v>
+        <v>124282327</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,42 +940,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bräcke kommun, Bräcke kommun, Jmt</t>
+          <t>Öramyran, Öramyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527679</v>
+        <v>527721</v>
       </c>
       <c r="R4" t="n">
-        <v>6963934</v>
+        <v>6963875</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,12 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:40</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hackspår, äldre.</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,27 +1023,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1061,7 +1061,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124282371</v>
+        <v>124282307</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527779</v>
+        <v>527724</v>
       </c>
       <c r="R5" t="n">
-        <v>6963815</v>
+        <v>6963869</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,22 +1131,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>08:49</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>08:49</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,48 +1147,23 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124282307</v>
+        <v>124282371</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1238,13 +1203,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527724</v>
+        <v>527779</v>
       </c>
       <c r="R6" t="n">
-        <v>6963869</v>
+        <v>6963815</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1268,12 +1233,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,16 +1259,41 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 18569-2025 artfynd.xlsx
+++ b/artfynd/A 18569-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124282403</v>
+        <v>124282089</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öramyran, Öramyran, Jmt</t>
+          <t>Bräcke kommun, Bräcke kommun, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527748</v>
+        <v>527679</v>
       </c>
       <c r="R2" t="n">
-        <v>6963833</v>
+        <v>6963934</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +750,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hackspår, äldre.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,26 +781,51 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124282089</v>
+        <v>124282371</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,42 +838,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bräcke kommun, Bräcke kommun, Jmt</t>
+          <t>Öramyran, Öramyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527679</v>
+        <v>527779</v>
       </c>
       <c r="R3" t="n">
-        <v>6963934</v>
+        <v>6963815</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +897,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +907,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:40</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hackspår, äldre.</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,7 +921,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -901,12 +936,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1061,7 +1096,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124282307</v>
+        <v>124282403</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1101,10 +1136,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527724</v>
+        <v>527748</v>
       </c>
       <c r="R5" t="n">
-        <v>6963869</v>
+        <v>6963833</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1163,7 +1198,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124282371</v>
+        <v>124282307</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1203,13 +1238,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527779</v>
+        <v>527724</v>
       </c>
       <c r="R6" t="n">
-        <v>6963815</v>
+        <v>6963869</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,22 +1268,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>08:49</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>08:49</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,41 +1284,16 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 18569-2025 artfynd.xlsx
+++ b/artfynd/A 18569-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124282089</v>
+        <v>124282327</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bräcke kommun, Bräcke kommun, Jmt</t>
+          <t>Öramyran, Öramyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527679</v>
+        <v>527721</v>
       </c>
       <c r="R2" t="n">
-        <v>6963934</v>
+        <v>6963875</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:40</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hackspår, äldre.</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,27 +774,27 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -959,7 +949,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124282327</v>
+        <v>124282403</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -999,13 +989,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527721</v>
+        <v>527748</v>
       </c>
       <c r="R4" t="n">
-        <v>6963875</v>
+        <v>6963833</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1029,22 +1019,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>08:46</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>08:46</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,51 +1035,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124282403</v>
+        <v>124282089</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1112,37 +1067,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öramyran, Öramyran, Jmt</t>
+          <t>Bräcke kommun, Bräcke kommun, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527748</v>
+        <v>527679</v>
       </c>
       <c r="R5" t="n">
-        <v>6963833</v>
+        <v>6963934</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1166,12 +1126,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hackspår, äldre.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1182,16 +1157,41 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 18569-2025 artfynd.xlsx
+++ b/artfynd/A 18569-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124282327</v>
+        <v>124282371</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527721</v>
+        <v>527779</v>
       </c>
       <c r="R2" t="n">
-        <v>6963875</v>
+        <v>6963815</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,22 +779,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124282371</v>
+        <v>124282089</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,37 +828,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öramyran, Öramyran, Jmt</t>
+          <t>Bräcke kommun, Bräcke kommun, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527779</v>
+        <v>527679</v>
       </c>
       <c r="R3" t="n">
-        <v>6963815</v>
+        <v>6963934</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +902,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hackspår, äldre.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,7 +921,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -926,12 +936,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -949,7 +959,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124282403</v>
+        <v>124282327</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -989,13 +999,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527748</v>
+        <v>527721</v>
       </c>
       <c r="R4" t="n">
-        <v>6963833</v>
+        <v>6963875</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1019,12 +1029,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,26 +1055,51 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124282089</v>
+        <v>124282307</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,42 +1112,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bräcke kommun, Bräcke kommun, Jmt</t>
+          <t>Öramyran, Öramyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527679</v>
+        <v>527724</v>
       </c>
       <c r="R5" t="n">
-        <v>6963934</v>
+        <v>6963869</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1126,27 +1166,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>08:40</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>08:40</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hackspår, äldre.</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,48 +1182,23 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124282307</v>
+        <v>124282403</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527724</v>
+        <v>527748</v>
       </c>
       <c r="R6" t="n">
-        <v>6963869</v>
+        <v>6963833</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 18569-2025 artfynd.xlsx
+++ b/artfynd/A 18569-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124282371</v>
+        <v>124282089</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öramyran, Öramyran, Jmt</t>
+          <t>Bräcke kommun, Bräcke kommun, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527779</v>
+        <v>527679</v>
       </c>
       <c r="R2" t="n">
-        <v>6963815</v>
+        <v>6963934</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hackspår, äldre.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +784,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -789,12 +799,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,10 +822,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124282089</v>
+        <v>124282371</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,42 +838,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bräcke kommun, Bräcke kommun, Jmt</t>
+          <t>Öramyran, Öramyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527679</v>
+        <v>527779</v>
       </c>
       <c r="R3" t="n">
-        <v>6963934</v>
+        <v>6963815</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +897,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,12 +907,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:40</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hackspår, äldre.</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,7 +921,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -936,12 +936,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -959,7 +959,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124282327</v>
+        <v>124282403</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -999,13 +999,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527721</v>
+        <v>527748</v>
       </c>
       <c r="R4" t="n">
-        <v>6963875</v>
+        <v>6963833</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1029,22 +1029,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>08:46</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>08:46</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,41 +1045,16 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1198,7 +1163,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124282403</v>
+        <v>124282327</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1238,13 +1203,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527748</v>
+        <v>527721</v>
       </c>
       <c r="R6" t="n">
-        <v>6963833</v>
+        <v>6963875</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1268,12 +1233,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,16 +1259,41 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 18569-2025 artfynd.xlsx
+++ b/artfynd/A 18569-2025 artfynd.xlsx
@@ -959,7 +959,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124282403</v>
+        <v>124282307</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527748</v>
+        <v>527724</v>
       </c>
       <c r="R4" t="n">
-        <v>6963833</v>
+        <v>6963869</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1061,7 +1061,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124282307</v>
+        <v>124282327</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527724</v>
+        <v>527721</v>
       </c>
       <c r="R5" t="n">
-        <v>6963869</v>
+        <v>6963875</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,12 +1131,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,23 +1157,48 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124282327</v>
+        <v>124282403</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1203,13 +1238,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527721</v>
+        <v>527748</v>
       </c>
       <c r="R6" t="n">
-        <v>6963875</v>
+        <v>6963833</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,22 +1268,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>08:46</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>08:46</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,41 +1284,16 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
